--- a/diseases/d013/2005-2009.xlsx
+++ b/diseases/d013/2005-2009.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1895,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2336,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2777,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3233,9 +3218,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3659,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4121,9 +4100,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4541,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5009,9 +4982,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5453,9 +5423,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5897,9 +5864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6341,9 +6305,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6785,9 +6746,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7181,9 +7139,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7580,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8069,9 +8021,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8462,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8903,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9401,9 +9344,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9845,9 +9785,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10226,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10733,9 +10667,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11177,9 +11108,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11621,9 +11549,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12065,9 +11990,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12509,9 +12431,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12905,9 +12824,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13349,9 +13265,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13793,9 +13706,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14237,9 +14147,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14681,9 +14588,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15125,9 +15029,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15569,9 +15470,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16013,9 +15911,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16457,9 +16352,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -16901,9 +16793,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17345,9 +17234,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17789,9 +17675,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18233,9 +18116,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18629,9 +18509,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19073,9 +18950,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19517,9 +19391,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -19961,9 +19832,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20405,9 +20273,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20849,9 +20714,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21293,9 +21155,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -21737,9 +21596,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22181,9 +22037,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -22625,9 +22478,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -23069,9 +22919,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23513,9 +23360,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -23957,9 +23801,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24353,9 +24194,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -24797,9 +24635,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25241,9 +25076,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -25685,9 +25517,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26129,9 +25958,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26573,9 +26399,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -27017,9 +26840,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -27461,9 +27281,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -27905,9 +27722,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -28349,9 +28163,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -28793,9 +28604,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -29235,9 +29043,6 @@
         <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q191" t="n">
         <v>0</v>
       </c>
       <c r="R191" t="n">
